--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484765_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484765_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8646</v>
+        <v>4.7046</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9508</v>
+        <v>5.6585</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0862</v>
+        <v>-0.9539</v>
       </c>
       <c r="G2" t="n">
         <v>3.6863</v>
@@ -610,13 +610,13 @@
         <v>0.5661</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1593</v>
+        <v>-0.0007</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5908</v>
+        <v>0.2985</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4315</v>
+        <v>-0.2992</v>
       </c>
       <c r="V2" t="n">
         <v>0.6415999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0935</v>
+        <v>2.9973</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3075</v>
+        <v>3.5024</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2141</v>
+        <v>-0.5051</v>
       </c>
       <c r="G3" t="n">
         <v>0.9426</v>
@@ -688,13 +688,13 @@
         <v>1.1322</v>
       </c>
       <c r="S3" t="n">
-        <v>0.264</v>
+        <v>0.1678</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1328</v>
+        <v>0.3277</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1312</v>
+        <v>-0.1598</v>
       </c>
       <c r="V3" t="n">
         <v>0.9434</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8884</v>
+        <v>2.6964</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6406</v>
+        <v>4.3428</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7522</v>
+        <v>-1.6464</v>
       </c>
       <c r="G4" t="n">
         <v>2.8867</v>
@@ -766,13 +766,13 @@
         <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2627</v>
+        <v>-0.4547</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.786</v>
+        <v>-0.0838</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4767</v>
+        <v>-0.3709</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2452</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>A. CABALLERO ROMERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8986</v>
+        <v>0.7096</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1468</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2482</v>
+        <v>0.1254</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0143</v>
+        <v>0.9948</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8197</v>
+        <v>0.5228</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.8054</v>
+        <v>0.472</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0367</v>
+        <v>1.8076</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4395</v>
+        <v>0.4915</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4028</v>
+        <v>1.3162</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.0224</v>
+        <v>-0.8128</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6198</v>
+        <v>0.0313</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.4026</v>
+        <v>-0.8442</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1887</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.887</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6983</v>
+        <v>0.9435</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3561</v>
+        <v>0.3565</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2802</v>
+        <v>0.3618</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0759</v>
+        <v>-0.0053</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2832</v>
+        <v>0.3018</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.2832</v>
+        <v>0.3018</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. MEJIA ACOSTA</t>
+          <t>S. BERGEMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8162</v>
+        <v>0.5839</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1896</v>
+        <v>0.6585</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3734</v>
+        <v>-0.0746</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.096</v>
+        <v>0.8143</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7163</v>
+        <v>0.5134</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8122</v>
+        <v>0.301</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0072</v>
+        <v>0.7173</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3032</v>
+        <v>0.6762</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.3103</v>
+        <v>0.0411</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0888</v>
+        <v>0.097</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5869</v>
+        <v>-0.1628</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4981</v>
+        <v>0.2598</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5913</v>
+        <v>-0.2304</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3855</v>
+        <v>-0.0588</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2058</v>
+        <v>-0.1716</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CABALLERO ROMERO</t>
+          <t>G. MEJIA ACOSTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7134</v>
+        <v>-0.4781</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.3715</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0069</v>
+        <v>-0.8496</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9948</v>
+        <v>-0.096</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5228</v>
+        <v>1.7163</v>
       </c>
       <c r="I8" t="n">
-        <v>0.472</v>
+        <v>-1.8122</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8076</v>
+        <v>-0.0072</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4915</v>
+        <v>2.3032</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3162</v>
+        <v>-2.3103</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8128</v>
+        <v>-0.0888</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0313</v>
+        <v>-0.5869</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8442</v>
+        <v>0.4981</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9435</v>
+        <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3603</v>
+        <v>0.297</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4979</v>
+        <v>0.5674</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1375</v>
+        <v>-0.2703</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3018</v>
+        <v>-1.2452</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. BERGEMAN</t>
+          <t>R. MOLLERMARK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.531</v>
+        <v>-0.5755</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6585</v>
+        <v>-0.4546</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1275</v>
+        <v>-0.1209</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8143</v>
+        <v>-0.5314</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5134</v>
+        <v>-0.1808</v>
       </c>
       <c r="I9" t="n">
-        <v>0.301</v>
+        <v>-0.3506</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7173</v>
+        <v>-0.5039</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6762</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0411</v>
+        <v>0.0823</v>
       </c>
       <c r="M9" t="n">
-        <v>0.097</v>
+        <v>-0.0275</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1628</v>
+        <v>0.4054</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2598</v>
+        <v>-0.4329</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2833</v>
+        <v>-0.0441</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0588</v>
+        <v>0.0493</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2246</v>
+        <v>-0.0934</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. MOLLERMARK</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1034</v>
+        <v>-0.6686</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9031</v>
+        <v>0.4261</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2003</v>
+        <v>-1.0947</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5314</v>
+        <v>0.0143</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1808</v>
+        <v>2.8197</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3506</v>
+        <v>-2.8054</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5039</v>
+        <v>3.0367</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5862000000000001</v>
+        <v>3.4395</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0823</v>
+        <v>-0.4028</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0275</v>
+        <v>-3.0224</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4054</v>
+        <v>-0.6198</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4329</v>
+        <v>-2.4026</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.572</v>
+        <v>0.7889</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3992</v>
+        <v>0.5596</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1728</v>
+        <v>0.2294</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2832</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.2832</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>M. VARELA BARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6886</v>
+        <v>-2.1134</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7167</v>
+        <v>-1.9878</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4053</v>
+        <v>-0.1256</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1356</v>
+        <v>0.762</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6394</v>
+        <v>1.0158</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7749</v>
+        <v>-0.2538</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2481</v>
+        <v>1.5823</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1745</v>
+        <v>1.49</v>
       </c>
       <c r="L11" t="n">
-        <v>2.0735</v>
+        <v>0.0922</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1125</v>
+        <v>-0.8203</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8139</v>
+        <v>-0.4742</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2986</v>
+        <v>-0.3461</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1887</v>
+        <v>-3.3966</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1322</v>
+        <v>-4.9062</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1451</v>
+        <v>-0.4222</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3992</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7459</v>
+        <v>-0.5131</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8678</v>
+        <v>0.9434</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8678</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. VARELA BARCIA</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4254</v>
+        <v>-2.1931</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9823</v>
+        <v>1.1064</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4431</v>
+        <v>-3.2995</v>
       </c>
       <c r="G12" t="n">
-        <v>0.762</v>
+        <v>0.1356</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0158</v>
+        <v>-0.6394</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2538</v>
+        <v>0.7749</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5823</v>
+        <v>2.2481</v>
       </c>
       <c r="K12" t="n">
-        <v>1.49</v>
+        <v>0.1745</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0922</v>
+        <v>2.0735</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8203</v>
+        <v>-2.1125</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4742</v>
+        <v>-0.8139</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3461</v>
+        <v>-1.2986</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.3966</v>
+        <v>0.1887</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.9062</v>
+        <v>-1.1322</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7341</v>
+        <v>-0.6496</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9036</v>
+        <v>-0.0094</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8306</v>
+        <v>-0.6401</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9434</v>
+        <v>-1.8678</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3018</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8134</v>
+        <v>-3.228</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4552</v>
+        <v>-3.2402</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3581</v>
+        <v>0.0122</v>
       </c>
       <c r="G13" t="n">
         <v>-3.931</v>
@@ -1468,13 +1468,13 @@
         <v>0.9435</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.505</v>
+        <v>0.0804</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1575</v>
+        <v>0.3725</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6625</v>
+        <v>-0.2921</v>
       </c>
       <c r="V13" t="n">
         <v>0.6226</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.0026</v>
+        <v>-4.0749</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.606</v>
+        <v>-2.9957</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3966</v>
+        <v>-1.0792</v>
       </c>
       <c r="G14" t="n">
         <v>-3.1269</v>
@@ -1546,13 +1546,13 @@
         <v>0.9435</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.234</v>
+        <v>-0.3063</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.2751</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8988</v>
+        <v>-0.5813</v>
       </c>
       <c r="V14" t="n">
         <v>0.3018</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.293800000000002</v>
+        <v>-0.7058999999999993</v>
       </c>
       <c r="E15" t="n">
-        <v>8.318100000000003</v>
+        <v>8.906000000000004</v>
       </c>
       <c r="F15" t="n">
         <v>-9.6119</v>
@@ -1591,10 +1591,10 @@
         <v>3.485200000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>5.76</v>
+        <v>5.760000000000002</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.2747</v>
+        <v>-2.274699999999999</v>
       </c>
       <c r="J15" t="n">
         <v>16.0065</v>
@@ -1603,7 +1603,7 @@
         <v>9.516299999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>6.490299999999999</v>
+        <v>6.4903</v>
       </c>
       <c r="M15" t="n">
         <v>-12.5213</v>
@@ -1624,13 +1624,13 @@
         <v>11.322</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0052</v>
+        <v>-0.4173999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1627</v>
+        <v>2.7508</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.168</v>
+        <v>-3.1677</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8868</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8475</v>
+        <v>3.8968</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9836</v>
+        <v>1.6913</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8639</v>
+        <v>2.2054</v>
       </c>
       <c r="G16" t="n">
         <v>1.9856</v>
@@ -1702,13 +1702,13 @@
         <v>1.6983</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6731</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2145</v>
+        <v>0.127</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3208</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5959</v>
+        <v>2.3987</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0648</v>
+        <v>2.8699</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4689</v>
+        <v>-0.4712</v>
       </c>
       <c r="G17" t="n">
         <v>2.3946</v>
@@ -1780,13 +1780,13 @@
         <v>1.887</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0317</v>
+        <v>0.8345</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8535</v>
+        <v>0.6586</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1782</v>
+        <v>0.1758</v>
       </c>
       <c r="V17" t="n">
         <v>0.3018</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. AGBEKO</t>
+          <t>S. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0264</v>
+        <v>0.9829</v>
       </c>
       <c r="E19" t="n">
-        <v>0.73</v>
+        <v>1.8953</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2964</v>
+        <v>-0.9124</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3072</v>
+        <v>2.2178</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0825</v>
+        <v>-0.5705</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2247</v>
+        <v>2.7883</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2497</v>
+        <v>3.5352</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7647</v>
+        <v>0.8773</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.485</v>
+        <v>2.6579</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0575</v>
+        <v>-1.3173</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3179</v>
+        <v>-1.4478</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2604</v>
+        <v>0.1304</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9435</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1322</v>
+        <v>1.6983</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7865</v>
+        <v>-0.1408</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5647</v>
+        <v>0.2471</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2217</v>
+        <v>-0.3879</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6036</v>
+        <v>-0.9054</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1824</v>
+        <v>0.6227</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7357</v>
+        <v>1.1255</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5534</v>
+        <v>-0.5028</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3457</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3962</v>
+        <v>0.0441</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2816</v>
+        <v>0.1081</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1146</v>
+        <v>-0.064</v>
       </c>
       <c r="V20" t="n">
         <v>1.8678</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. JIMENA LLORCA</t>
+          <t>R. AGBEKO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4676</v>
+        <v>0.1749</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3107</v>
+        <v>-0.2444</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7783</v>
+        <v>0.4193</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2178</v>
+        <v>-2.3072</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5705</v>
+        <v>-2.0825</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7883</v>
+        <v>-0.2247</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5352</v>
+        <v>-1.2497</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8773</v>
+        <v>-0.7647</v>
       </c>
       <c r="L21" t="n">
-        <v>2.6579</v>
+        <v>-0.485</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3173</v>
+        <v>-1.0575</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4478</v>
+        <v>-1.3179</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1304</v>
+        <v>0.2604</v>
       </c>
       <c r="P21" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.1887</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.887</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.6983</v>
+        <v>1.1322</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5913</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3375</v>
+        <v>0.5904</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2538</v>
+        <v>0.3446</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9054</v>
+        <v>0.6036</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>A. KLEINJAN RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6974</v>
+        <v>-0.3452</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0682</v>
+        <v>-0.387</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6292</v>
+        <v>0.0418</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7255</v>
+        <v>-2.1828</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1213</v>
+        <v>-4.0813</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.6042</v>
+        <v>1.8985</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4362</v>
+        <v>0.3744</v>
       </c>
       <c r="K22" t="n">
-        <v>0.09</v>
+        <v>-2.2594</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5262</v>
+        <v>2.6338</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2894</v>
+        <v>-2.5571</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2113</v>
+        <v>-1.8219</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.0781</v>
+        <v>-0.7353</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7548</v>
+        <v>2.2644</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2733</v>
+        <v>0.4037</v>
       </c>
       <c r="T22" t="n">
-        <v>0.368</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0946</v>
+        <v>0.3346</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. KLEINJAN RODRIGUEZ</t>
+          <t>T. DESPLACE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7082</v>
+        <v>-1.0816</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6536</v>
+        <v>0.2349</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0545</v>
+        <v>-1.3166</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1828</v>
+        <v>-0.4697</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.0813</v>
+        <v>0.5149</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8985</v>
+        <v>-0.9846</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3744</v>
+        <v>2.0713</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.2594</v>
+        <v>2.5152</v>
       </c>
       <c r="L23" t="n">
-        <v>2.6338</v>
+        <v>-0.4439</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5571</v>
+        <v>-2.541</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8219</v>
+        <v>-2.0003</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7353</v>
+        <v>-0.5407</v>
       </c>
       <c r="P23" t="n">
         <v>0.1887</v>
@@ -2248,28 +2248,28 @@
         <v>2.2644</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9593</v>
+        <v>0.4445</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1975</v>
+        <v>0.2393</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2382</v>
+        <v>0.2052</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2452</v>
+        <v>-1.2452</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. DESPLACE</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7178</v>
+        <v>-1.742</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3324</v>
+        <v>-0.1657</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0502</v>
+        <v>-1.5763</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4697</v>
+        <v>-2.7255</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5149</v>
+        <v>-0.1213</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9846</v>
+        <v>-2.6042</v>
       </c>
       <c r="J24" t="n">
-        <v>2.0713</v>
+        <v>-0.4362</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5152</v>
+        <v>0.09</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4439</v>
+        <v>-0.5262</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.541</v>
+        <v>-2.2894</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.0003</v>
+        <v>-0.2113</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5407</v>
+        <v>-2.0781</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2644</v>
+        <v>0.7548</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1917</v>
+        <v>0.2288</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3367</v>
+        <v>0.2705</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5284</v>
+        <v>-0.0417</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9352</v>
+        <v>-3.183</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0088</v>
+        <v>0.4242</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.944</v>
+        <v>-3.6072</v>
       </c>
       <c r="G25" t="n">
         <v>-4.2202</v>
@@ -2404,13 +2404,13 @@
         <v>1.5096</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3791</v>
+        <v>0.1314</v>
       </c>
       <c r="T25" t="n">
-        <v>0.974</v>
+        <v>0.3894</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5948</v>
+        <v>-0.258</v>
       </c>
       <c r="V25" t="n">
         <v>0.3398</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.293800000000001</v>
+        <v>3.892</v>
       </c>
       <c r="E26" t="n">
-        <v>9.612000000000002</v>
+        <v>9.611800000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.318200000000001</v>
+        <v>-5.720000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.4853</v>
+        <v>-3.485299999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.759999999999999</v>
+        <v>-5.76</v>
       </c>
       <c r="I26" t="n">
         <v>2.2748</v>
@@ -2482,13 +2482,13 @@
         <v>13.209</v>
       </c>
       <c r="S26" t="n">
-        <v>1.0052</v>
+        <v>3.6035</v>
       </c>
       <c r="T26" t="n">
-        <v>3.167899999999999</v>
+        <v>3.1678</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.1626</v>
+        <v>0.4356000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>1.8868</v>
